--- a/output_data/charts/1600000US3914184.xlsx
+++ b/output_data/charts/1600000US3914184.xlsx
@@ -207,7 +207,7 @@
                   <c:v>21979</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>22038</c:v>
+                  <c:v>22041</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -672,7 +672,7 @@
         <v>44013</v>
       </c>
       <c r="B6" s="2">
-        <v>22038</v>
+        <v>22041</v>
       </c>
     </row>
   </sheetData>
